--- a/research/traditional_assets/database/data/austria/austria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04705</v>
+        <v>0.0442</v>
       </c>
       <c r="E2">
-        <v>0.13</v>
+        <v>0.1588</v>
       </c>
       <c r="G2">
-        <v>0.0593436318767001</v>
+        <v>0.08785493917612015</v>
       </c>
       <c r="H2">
-        <v>0.0593436318767001</v>
+        <v>0.08785493917612015</v>
       </c>
       <c r="I2">
-        <v>0.0662222244651806</v>
+        <v>0.06648798708391723</v>
       </c>
       <c r="J2">
-        <v>0.04788314243456563</v>
+        <v>0.0553654941684612</v>
       </c>
       <c r="K2">
-        <v>561.2</v>
+        <v>703.7</v>
       </c>
       <c r="L2">
-        <v>0.02832183536797695</v>
+        <v>0.03749607029247681</v>
       </c>
       <c r="M2">
-        <v>65.59999999999999</v>
+        <v>176.4</v>
       </c>
       <c r="N2">
-        <v>0.01022842441724487</v>
+        <v>0.03294855990137846</v>
       </c>
       <c r="O2">
-        <v>0.1168923734853884</v>
+        <v>0.2506750035526503</v>
       </c>
       <c r="P2">
-        <v>65.59999999999999</v>
+        <v>176.4</v>
       </c>
       <c r="Q2">
-        <v>0.01022842441724487</v>
+        <v>0.03294855990137846</v>
       </c>
       <c r="R2">
-        <v>0.1168923734853884</v>
+        <v>0.2506750035526503</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4246.099999999999</v>
+        <v>3065.3</v>
       </c>
       <c r="V2">
-        <v>0.6620565993607234</v>
+        <v>0.5725466024132392</v>
       </c>
       <c r="W2">
-        <v>0.05715280672385143</v>
+        <v>0.06932212687424028</v>
       </c>
       <c r="X2">
-        <v>0.06114550801243607</v>
+        <v>0.1005575716988335</v>
       </c>
       <c r="Y2">
-        <v>-0.003992701288584644</v>
+        <v>-0.03123544482459324</v>
       </c>
       <c r="Z2">
-        <v>2.018447590913721</v>
+        <v>1.870687678797484</v>
       </c>
       <c r="AA2">
-        <v>0.09570236998895625</v>
+        <v>0.1022598268527366</v>
       </c>
       <c r="AB2">
-        <v>0.04553199264641479</v>
+        <v>0.07562560427128492</v>
       </c>
       <c r="AC2">
-        <v>0.05017037734254146</v>
+        <v>0.02663422258145172</v>
       </c>
       <c r="AD2">
-        <v>3818.6</v>
+        <v>3617.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3818.6</v>
+        <v>3617.5</v>
       </c>
       <c r="AG2">
-        <v>-427.4999999999991</v>
+        <v>552.1999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.3731980727318928</v>
+        <v>0.4032303010711937</v>
       </c>
       <c r="AI2">
-        <v>0.2669658899445598</v>
+        <v>0.3655812919395262</v>
       </c>
       <c r="AJ2">
-        <v>-0.07141663882392232</v>
+        <v>0.09349813748730101</v>
       </c>
       <c r="AK2">
-        <v>-0.04250517021953538</v>
+        <v>0.08085037848284746</v>
       </c>
       <c r="AL2">
-        <v>190.3</v>
+        <v>327.8</v>
       </c>
       <c r="AM2">
-        <v>190.3</v>
+        <v>327.8</v>
       </c>
       <c r="AN2">
-        <v>2.661787257772202</v>
+        <v>2.507451306577944</v>
       </c>
       <c r="AO2">
-        <v>6.895428271150815</v>
+        <v>3.806589383770592</v>
       </c>
       <c r="AP2">
-        <v>-0.2979924717691336</v>
+        <v>0.3827545574270464</v>
       </c>
       <c r="AQ2">
-        <v>6.895428271150815</v>
+        <v>3.806589383770592</v>
       </c>
     </row>
     <row r="3">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0221</v>
+        <v>0.0372</v>
       </c>
       <c r="E3">
-        <v>0.3720000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="G3">
-        <v>0.06697132183093306</v>
+        <v>0.08013415847249486</v>
       </c>
       <c r="H3">
-        <v>0.06697132183093306</v>
+        <v>0.08013415847249486</v>
       </c>
       <c r="I3">
-        <v>0.06749668520726836</v>
+        <v>0.06611090081604268</v>
       </c>
       <c r="J3">
-        <v>0.05049789874151057</v>
+        <v>0.05042815133820842</v>
       </c>
       <c r="K3">
-        <v>383.8</v>
+        <v>395.7</v>
       </c>
       <c r="L3">
-        <v>0.03200547045039485</v>
+        <v>0.03483366638203474</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3325.2</v>
+        <v>2354.4</v>
       </c>
       <c r="V3">
-        <v>0.9214398536869233</v>
+        <v>0.7700660692091319</v>
       </c>
       <c r="W3">
-        <v>0.06632335660468652</v>
+        <v>0.06089003785430708</v>
       </c>
       <c r="X3">
-        <v>0.05773363558648091</v>
+        <v>0.09641488586199547</v>
       </c>
       <c r="Y3">
-        <v>0.008589721018205612</v>
+        <v>-0.03552484800768839</v>
       </c>
       <c r="Z3">
-        <v>2.120473192813694</v>
+        <v>2.334168944048328</v>
       </c>
       <c r="AA3">
-        <v>0.1070794405747935</v>
+        <v>0.1177078247594152</v>
       </c>
       <c r="AB3">
-        <v>0.04569628263315412</v>
+        <v>0.07604310200645478</v>
       </c>
       <c r="AC3">
-        <v>0.06138315794163938</v>
+        <v>0.04166472275296046</v>
       </c>
       <c r="AD3">
-        <v>1693.3</v>
+        <v>1712.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1693.3</v>
+        <v>1712.1</v>
       </c>
       <c r="AG3">
-        <v>-1631.9</v>
+        <v>-642.3000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.3193700490380988</v>
+        <v>0.3589684453296991</v>
       </c>
       <c r="AI3">
-        <v>0.2067041834006763</v>
+        <v>0.2897444576070401</v>
       </c>
       <c r="AJ3">
-        <v>-0.8255261027923917</v>
+        <v>-0.2659517204256553</v>
       </c>
       <c r="AK3">
-        <v>-0.3353196210984856</v>
+        <v>-0.1806954368986666</v>
       </c>
       <c r="AL3">
-        <v>105.2</v>
+        <v>197</v>
       </c>
       <c r="AM3">
-        <v>105.2</v>
+        <v>197</v>
       </c>
       <c r="AN3">
-        <v>2.016553531022984</v>
+        <v>2.078043451875228</v>
       </c>
       <c r="AO3">
-        <v>7.693916349809886</v>
+        <v>3.812182741116751</v>
       </c>
       <c r="AP3">
-        <v>-1.943432178158866</v>
+        <v>-0.7795849010802284</v>
       </c>
       <c r="AQ3">
-        <v>7.693916349809886</v>
+        <v>3.812182741116751</v>
       </c>
     </row>
     <row r="4">
@@ -853,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07200000000000001</v>
+        <v>0.0512</v>
       </c>
       <c r="E4">
-        <v>-0.112</v>
+        <v>0.244</v>
       </c>
       <c r="G4">
-        <v>0.04765191604673161</v>
+        <v>0.09969490793239376</v>
       </c>
       <c r="H4">
-        <v>0.04765191604673161</v>
+        <v>0.09969490793239376</v>
       </c>
       <c r="I4">
-        <v>0.06426873226474424</v>
+        <v>0.06706625627733678</v>
       </c>
       <c r="J4">
-        <v>0.04485837756677413</v>
+        <v>0.06053717581993593</v>
       </c>
       <c r="K4">
-        <v>177.4</v>
+        <v>308</v>
       </c>
       <c r="L4">
-        <v>0.02267556305442647</v>
+        <v>0.04157891894810735</v>
       </c>
       <c r="M4">
-        <v>65.59999999999999</v>
+        <v>176.4</v>
       </c>
       <c r="N4">
-        <v>0.02338847689674843</v>
+        <v>0.07681588573419265</v>
       </c>
       <c r="O4">
-        <v>0.3697857948139797</v>
+        <v>0.5727272727272728</v>
       </c>
       <c r="P4">
-        <v>65.59999999999999</v>
+        <v>176.4</v>
       </c>
       <c r="Q4">
-        <v>0.02338847689674843</v>
+        <v>0.07681588573419265</v>
       </c>
       <c r="R4">
-        <v>0.3697857948139797</v>
+        <v>0.5727272727272728</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>920.9</v>
+        <v>710.9</v>
       </c>
       <c r="V4">
-        <v>0.3283300057045065</v>
+        <v>0.3095715032224351</v>
       </c>
       <c r="W4">
-        <v>0.04798225684301634</v>
+        <v>0.07775421589417349</v>
       </c>
       <c r="X4">
-        <v>0.06455738043839124</v>
+        <v>0.1047002575356716</v>
       </c>
       <c r="Y4">
-        <v>-0.0165751235953749</v>
+        <v>-0.02694604164149808</v>
       </c>
       <c r="Z4">
-        <v>1.879811619972127</v>
+        <v>1.434025089050643</v>
       </c>
       <c r="AA4">
-        <v>0.08432529940311899</v>
+        <v>0.08681182894605805</v>
       </c>
       <c r="AB4">
-        <v>0.04536770265967546</v>
+        <v>0.07520810653611507</v>
       </c>
       <c r="AC4">
-        <v>0.03895759674344353</v>
+        <v>0.01160372240994298</v>
       </c>
       <c r="AD4">
-        <v>2125.3</v>
+        <v>1905.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2125.3</v>
+        <v>1905.4</v>
       </c>
       <c r="AG4">
-        <v>1204.4</v>
+        <v>1194.5</v>
       </c>
       <c r="AH4">
-        <v>0.4310865905356889</v>
+        <v>0.4534723213860726</v>
       </c>
       <c r="AI4">
-        <v>0.3477371641742204</v>
+        <v>0.4779990968842506</v>
       </c>
       <c r="AJ4">
-        <v>0.300409059163923</v>
+        <v>0.34217537024836</v>
       </c>
       <c r="AK4">
-        <v>0.2320214221040668</v>
+        <v>0.3646994168473117</v>
       </c>
       <c r="AL4">
-        <v>85.09999999999999</v>
+        <v>130.8</v>
       </c>
       <c r="AM4">
-        <v>85.09999999999999</v>
+        <v>130.8</v>
       </c>
       <c r="AN4">
-        <v>3.572533198856951</v>
+        <v>3.079185520361991</v>
       </c>
       <c r="AO4">
-        <v>5.90834312573443</v>
+        <v>3.798165137614679</v>
       </c>
       <c r="AP4">
-        <v>2.024541939821819</v>
+        <v>1.930349062702004</v>
       </c>
       <c r="AQ4">
-        <v>5.90834312573443</v>
+        <v>3.798165137614679</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0442</v>
+        <v>0.0741</v>
       </c>
       <c r="E2">
-        <v>0.1588</v>
+        <v>0.1495</v>
       </c>
       <c r="G2">
-        <v>0.08785493917612015</v>
+        <v>0.06284721512519162</v>
       </c>
       <c r="H2">
-        <v>0.08785493917612015</v>
+        <v>0.06284721512519162</v>
       </c>
       <c r="I2">
-        <v>0.06648798708391723</v>
+        <v>0.158757281553398</v>
       </c>
       <c r="J2">
-        <v>0.0553654941684612</v>
+        <v>0.1326777379737813</v>
       </c>
       <c r="K2">
-        <v>703.7</v>
+        <v>1133.3</v>
       </c>
       <c r="L2">
-        <v>0.03749607029247681</v>
+        <v>0.04632805314256515</v>
       </c>
       <c r="M2">
-        <v>176.4</v>
+        <v>217.8</v>
       </c>
       <c r="N2">
-        <v>0.03294855990137846</v>
+        <v>0.03467876761404347</v>
       </c>
       <c r="O2">
-        <v>0.2506750035526503</v>
+        <v>0.1921821230036178</v>
       </c>
       <c r="P2">
-        <v>176.4</v>
+        <v>217.8</v>
       </c>
       <c r="Q2">
-        <v>0.03294855990137846</v>
+        <v>0.03467876761404347</v>
       </c>
       <c r="R2">
-        <v>0.2506750035526503</v>
+        <v>0.1921821230036178</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3065.3</v>
+        <v>2721.3</v>
       </c>
       <c r="V2">
-        <v>0.5725466024132392</v>
+        <v>0.4332935275853834</v>
       </c>
       <c r="W2">
-        <v>0.06932212687424028</v>
+        <v>0.1319149396440335</v>
       </c>
       <c r="X2">
-        <v>0.1005575716988335</v>
+        <v>0.08999901999896759</v>
       </c>
       <c r="Y2">
-        <v>-0.03123544482459324</v>
+        <v>0.04191591964506591</v>
       </c>
       <c r="Z2">
-        <v>1.870687678797484</v>
+        <v>2.54929239875779</v>
       </c>
       <c r="AA2">
-        <v>0.1022598268527366</v>
+        <v>0.3413437504183654</v>
       </c>
       <c r="AB2">
-        <v>0.07562560427128492</v>
+        <v>0.06714996910573551</v>
       </c>
       <c r="AC2">
-        <v>0.02663422258145172</v>
+        <v>0.2741937813126299</v>
       </c>
       <c r="AD2">
-        <v>3617.5</v>
+        <v>4852.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3617.5</v>
+        <v>4852.1</v>
       </c>
       <c r="AG2">
-        <v>552.1999999999998</v>
+        <v>2130.8</v>
       </c>
       <c r="AH2">
-        <v>0.4032303010711937</v>
+        <v>0.4358460736934768</v>
       </c>
       <c r="AI2">
-        <v>0.3655812919395262</v>
+        <v>0.3512476563461441</v>
       </c>
       <c r="AJ2">
-        <v>0.09349813748730101</v>
+        <v>0.2533258830382938</v>
       </c>
       <c r="AK2">
-        <v>0.08085037848284746</v>
+        <v>0.1920920253141735</v>
       </c>
       <c r="AL2">
-        <v>327.8</v>
+        <v>281.6</v>
       </c>
       <c r="AM2">
-        <v>327.8</v>
+        <v>281.6</v>
       </c>
       <c r="AN2">
-        <v>2.507451306577944</v>
+        <v>2.038954490061773</v>
       </c>
       <c r="AO2">
-        <v>3.806589383770592</v>
+        <v>13.79119318181818</v>
       </c>
       <c r="AP2">
-        <v>0.3827545574270464</v>
+        <v>0.8954069840736228</v>
       </c>
       <c r="AQ2">
-        <v>3.806589383770592</v>
+        <v>13.79119318181818</v>
       </c>
     </row>
     <row r="3">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0372</v>
+        <v>0.0901</v>
       </c>
       <c r="E3">
-        <v>0.0736</v>
+        <v>0.181</v>
       </c>
       <c r="G3">
-        <v>0.08013415847249486</v>
+        <v>0.05693422675276866</v>
       </c>
       <c r="H3">
-        <v>0.08013415847249486</v>
+        <v>0.05693422675276866</v>
       </c>
       <c r="I3">
-        <v>0.06611090081604268</v>
+        <v>0.2007277763940442</v>
       </c>
       <c r="J3">
-        <v>0.05042815133820842</v>
+        <v>0.1634261848803407</v>
       </c>
       <c r="K3">
-        <v>395.7</v>
+        <v>722.6</v>
       </c>
       <c r="L3">
-        <v>0.03483366638203474</v>
+        <v>0.04389743091287946</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>217.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05809084362414317</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3014115693329643</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>217.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05809084362414317</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3014115693329643</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2354.4</v>
+        <v>1936.7</v>
       </c>
       <c r="V3">
-        <v>0.7700660692091319</v>
+        <v>0.5165497559544449</v>
       </c>
       <c r="W3">
-        <v>0.06089003785430708</v>
+        <v>0.1246614336237385</v>
       </c>
       <c r="X3">
-        <v>0.09641488586199547</v>
+        <v>0.09010792205054027</v>
       </c>
       <c r="Y3">
-        <v>-0.03552484800768839</v>
+        <v>0.03455351157319819</v>
       </c>
       <c r="Z3">
-        <v>2.334168944048328</v>
+        <v>3.567178086941446</v>
       </c>
       <c r="AA3">
-        <v>0.1177078247594152</v>
+        <v>0.5829703055375929</v>
       </c>
       <c r="AB3">
-        <v>0.07604310200645478</v>
+        <v>0.06713723263887419</v>
       </c>
       <c r="AC3">
-        <v>0.04166472275296046</v>
+        <v>0.5158330728987187</v>
       </c>
       <c r="AD3">
-        <v>1712.1</v>
+        <v>2910</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1712.1</v>
+        <v>2910</v>
       </c>
       <c r="AG3">
-        <v>-642.3000000000002</v>
+        <v>973.3</v>
       </c>
       <c r="AH3">
-        <v>0.3589684453296991</v>
+        <v>0.436982866067004</v>
       </c>
       <c r="AI3">
-        <v>0.2897444576070401</v>
+        <v>0.3089663959229176</v>
       </c>
       <c r="AJ3">
-        <v>-0.2659517204256553</v>
+        <v>0.2060941007072375</v>
       </c>
       <c r="AK3">
-        <v>-0.1806954368986666</v>
+        <v>0.1300890160121896</v>
       </c>
       <c r="AL3">
-        <v>197</v>
+        <v>226.1</v>
       </c>
       <c r="AM3">
-        <v>197</v>
+        <v>226.1</v>
       </c>
       <c r="AN3">
-        <v>2.078043451875228</v>
+        <v>1.702152550304165</v>
       </c>
       <c r="AO3">
-        <v>3.812182741116751</v>
+        <v>14.61388766032729</v>
       </c>
       <c r="AP3">
-        <v>-0.7795849010802284</v>
+        <v>0.5693144595226953</v>
       </c>
       <c r="AQ3">
-        <v>3.812182741116751</v>
+        <v>14.61388766032729</v>
       </c>
     </row>
     <row r="4">
@@ -853,121 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0512</v>
+        <v>0.0581</v>
       </c>
       <c r="E4">
-        <v>0.244</v>
+        <v>0.118</v>
       </c>
       <c r="G4">
-        <v>0.09969490793239376</v>
+        <v>0.07501187292223861</v>
       </c>
       <c r="H4">
-        <v>0.09969490793239376</v>
+        <v>0.07501187292223861</v>
       </c>
       <c r="I4">
-        <v>0.06706625627733678</v>
+        <v>0.07241232784262754</v>
       </c>
       <c r="J4">
-        <v>0.06053717581993593</v>
+        <v>0.06207804799460914</v>
       </c>
       <c r="K4">
-        <v>308</v>
+        <v>410.7</v>
       </c>
       <c r="L4">
-        <v>0.04157891894810735</v>
+        <v>0.05132851750943585</v>
       </c>
       <c r="M4">
-        <v>176.4</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07681588573419265</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5727272727272728</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>176.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07681588573419265</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.5727272727272728</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>710.9</v>
+        <v>784.6</v>
       </c>
       <c r="V4">
-        <v>0.3095715032224351</v>
+        <v>0.3099715549936789</v>
       </c>
       <c r="W4">
-        <v>0.07775421589417349</v>
+        <v>0.1391684456643286</v>
       </c>
       <c r="X4">
-        <v>0.1047002575356716</v>
+        <v>0.08989011794739489</v>
       </c>
       <c r="Y4">
-        <v>-0.02694604164149808</v>
+        <v>0.04927832771693368</v>
       </c>
       <c r="Z4">
-        <v>1.434025089050643</v>
+        <v>1.606319762306271</v>
       </c>
       <c r="AA4">
-        <v>0.08681182894605805</v>
+        <v>0.09971719529913788</v>
       </c>
       <c r="AB4">
-        <v>0.07520810653611507</v>
+        <v>0.06716270557259681</v>
       </c>
       <c r="AC4">
-        <v>0.01160372240994298</v>
+        <v>0.03255448972654107</v>
       </c>
       <c r="AD4">
-        <v>1905.4</v>
+        <v>1942.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1905.4</v>
+        <v>1942.1</v>
       </c>
       <c r="AG4">
-        <v>1194.5</v>
+        <v>1157.5</v>
       </c>
       <c r="AH4">
-        <v>0.4534723213860726</v>
+        <v>0.4341537567344019</v>
       </c>
       <c r="AI4">
-        <v>0.4779990968842506</v>
+        <v>0.4418482959457615</v>
       </c>
       <c r="AJ4">
-        <v>0.34217537024836</v>
+        <v>0.3137961883590425</v>
       </c>
       <c r="AK4">
-        <v>0.3646994168473117</v>
+        <v>0.3205660795391603</v>
       </c>
       <c r="AL4">
-        <v>130.8</v>
+        <v>55.5</v>
       </c>
       <c r="AM4">
-        <v>130.8</v>
+        <v>55.5</v>
       </c>
       <c r="AN4">
-        <v>3.079185520361991</v>
+        <v>2.898224145649903</v>
       </c>
       <c r="AO4">
-        <v>3.798165137614679</v>
+        <v>10.43963963963964</v>
       </c>
       <c r="AP4">
-        <v>1.930349062702004</v>
+        <v>1.727354126249813</v>
       </c>
       <c r="AQ4">
-        <v>3.798165137614679</v>
+        <v>10.43963963963964</v>
       </c>
     </row>
   </sheetData>
